--- a/templates/template.xlsx
+++ b/templates/template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\b-kaori.uchiyama\Desktop\cloud-security-diagnosis\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01803604-0466-402D-B2FA-026EBACCF817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D7A77EF-468C-4F51-8263-9BDA54CA3D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="基本情報" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="62">
   <si>
     <t>質問</t>
   </si>
@@ -72,18 +72,9 @@
     <t>はい</t>
   </si>
   <si>
-    <t>AWSの画面を人が操作する場合は「はい」。分からない場合は空欄</t>
-  </si>
-  <si>
     <t>AWS管理画面を利用する目的は何ですか？</t>
   </si>
   <si>
-    <t>システムの設定変更・確認</t>
-  </si>
-  <si>
-    <t>分かる範囲で記入。分からない場合は空欄</t>
-  </si>
-  <si>
     <t>SSOなどAWSへログインするための別の仕組みを利用していますか？</t>
   </si>
   <si>
@@ -94,9 +85,6 @@
   </si>
   <si>
     <t>検証用アカウントのため</t>
-  </si>
-  <si>
-    <t>理由が分かる場合のみ記入。分からない場合は空欄</t>
   </si>
   <si>
     <t>MFAを設定していない利用者がいる場合、理由はありますか？</t>
@@ -135,6 +123,251 @@
   </si>
   <si>
     <t>診断用Role ARN（入力必須）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>システムの設定変更・確認、障害対応用</t>
+    <rPh sb="13" eb="15">
+      <t>ショウガイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ヨウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>管理画面を利用する主な用途を分かる範囲で記入。分からない場合は空欄</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>IAMユーザーによるログイン利用の有無をプルダウン選択。分からない場合は空欄</t>
+    <rPh sb="25" eb="27">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>クウラン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>理由が分かる場合のみ記入。分からない場合や該当者がいない場合は空欄</t>
+    <rPh sb="21" eb="24">
+      <t>ガイトウシャ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>管理者権限</t>
+    <rPh sb="0" eb="5">
+      <t>カンリシャケンゲン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>「はい」の場合、その権限は誰が・何のために使用していますか？</t>
+  </si>
+  <si>
+    <t>はい</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>運用担当者が障害対応や設定変更のために使用</t>
+  </si>
+  <si>
+    <t>プルダウンから選択。不明時は空欄</t>
+    <rPh sb="7" eb="9">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>フメイジ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>クウラン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>未使用IAM</t>
+    <rPh sb="0" eb="3">
+      <t>ミシヨウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>長期間利用していないIAMユーザーを残している場合、その理由を教えてください。</t>
+  </si>
+  <si>
+    <t>緊急時の保守作業用として残している</t>
+  </si>
+  <si>
+    <t>備考</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>理由が不明、概要がない場合には空欄</t>
+    <rPh sb="0" eb="2">
+      <t>リユウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>フメイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ガイヨウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>クウラン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>アクセスキー</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>複数のアクセスキーを持つ運用をしている場合、その目的を教えてください。</t>
+  </si>
+  <si>
+    <t>長期間利用していないアクセスキーを残すことはありますか？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>いいえ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>定期的なキー交換の際に一時的に2つ使用するため</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>複数アクセスキーを持つ運用をしていない、もしくは不明な時は空欄</t>
+    <rPh sb="0" eb="2">
+      <t>フクスウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ウンヨウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>フメイ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>クウラン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>分からないときは空欄</t>
+    <rPh sb="0" eb="1">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>クウラン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Trust Policy</t>
+  </si>
+  <si>
+    <t>Roleを別のAWSアカウントや外部サービスから利用していますか？</t>
+  </si>
+  <si>
+    <t>利用している場合、どこから・何のために利用していますか？</t>
+  </si>
+  <si>
+    <t>別のAWSアカウントからシステム運用のために利用</t>
+  </si>
+  <si>
+    <t>どこから・何のためにをわかる範囲で記入。外部サービスを使ってない、内容が分からないときは空欄</t>
+    <rPh sb="5" eb="6">
+      <t>ナン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>キニュウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ガイブ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>クウラン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Permission Boundary</t>
+  </si>
+  <si>
+    <t>利用者やRoleに付与する権限を制限する仕組みを利用していますか？</t>
+  </si>
+  <si>
+    <t>権限を制限するために、どのようなルールや運用をしていますか？</t>
+  </si>
+  <si>
+    <t>開発者が自由に管理者権限を付けられないよう制限している</t>
+  </si>
+  <si>
+    <t>Permission Boundaryなど。分からない場合は空欄</t>
+    <rPh sb="30" eb="32">
+      <t>クウラン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>仕組みの名前が分からなくても、わかる範囲で運用方法を記入。不明時や使用してない場合は空欄</t>
+    <rPh sb="18" eb="20">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="29" eb="32">
+      <t>フメイジ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>クウラン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>管理者権限（設定を幅広く変更できる権限）を持つ利用者・Roleはありますか？</t>
+    <rPh sb="17" eb="19">
+      <t>ケンゲン</t>
+    </rPh>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -203,7 +436,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -216,6 +449,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -544,38 +783,38 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.15">
@@ -592,14 +831,14 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -611,10 +850,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E144"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="1" max="1" width="18.375" customWidth="1"/>
     <col min="2" max="2" width="58" customWidth="1"/>
     <col min="3" max="3" width="26" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
@@ -635,7 +874,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="27" x14ac:dyDescent="0.15">
@@ -650,22 +889,22 @@
         <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="27" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="27" x14ac:dyDescent="0.15">
@@ -673,36 +912,937 @@
         <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="27" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>23</v>
-      </c>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="27" x14ac:dyDescent="0.15">
+      <c r="A7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="27" x14ac:dyDescent="0.15">
+      <c r="A8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="27" x14ac:dyDescent="0.15">
+      <c r="A9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="27" x14ac:dyDescent="0.15">
+      <c r="A14" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A15" s="6"/>
+      <c r="B15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A16" s="6"/>
+      <c r="B16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A17" s="6"/>
+      <c r="B17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A18" s="6"/>
+      <c r="B18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A19" s="6"/>
+      <c r="B19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A20" s="6"/>
+      <c r="B20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A21" s="6"/>
+      <c r="B21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A22" s="6"/>
+      <c r="B22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A23" s="6"/>
+      <c r="B23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A24" s="6"/>
+      <c r="B24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A25" s="6"/>
+      <c r="B25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A26" s="6"/>
+      <c r="B26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A27" s="6"/>
+      <c r="B27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A28" s="6"/>
+      <c r="B28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A29" s="6"/>
+      <c r="B29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A30" s="6"/>
+      <c r="B30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A31" s="6"/>
+      <c r="B31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A32" s="6"/>
+      <c r="B32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A33" s="6"/>
+      <c r="B33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A34" s="6"/>
+      <c r="B34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A35" s="6"/>
+      <c r="B35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A36" s="6"/>
+      <c r="B36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A37" s="6"/>
+      <c r="B37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A38" s="6"/>
+      <c r="B38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A39" s="6"/>
+      <c r="B39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A40" s="6"/>
+      <c r="B40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A41" s="6"/>
+      <c r="B41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A42" s="6"/>
+      <c r="B42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A43" s="6"/>
+      <c r="B43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A44" s="6"/>
+      <c r="B44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A45" s="6"/>
+      <c r="B45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A46" s="6"/>
+      <c r="B46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A47" s="6"/>
+      <c r="B47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A48" s="6"/>
+      <c r="B48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A49" s="6"/>
+      <c r="B49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A50" s="6"/>
+      <c r="B50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A51" s="6"/>
+      <c r="B51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A52" s="6"/>
+      <c r="B52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A53" s="6"/>
+      <c r="B53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A54" s="6"/>
+      <c r="B54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A55" s="6"/>
+      <c r="B55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A56" s="6"/>
+      <c r="B56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A57" s="6"/>
+      <c r="B57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A58" s="6"/>
+      <c r="B58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A59" s="6"/>
+      <c r="B59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A60" s="6"/>
+      <c r="B60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A61" s="6"/>
+      <c r="B61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A62" s="6"/>
+      <c r="B62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A63" s="6"/>
+      <c r="B63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A64" s="6"/>
+      <c r="B64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A65" s="6"/>
+      <c r="B65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A66" s="6"/>
+      <c r="B66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A67" s="6"/>
+      <c r="B67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A68" s="6"/>
+      <c r="B68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A69" s="6"/>
+      <c r="B69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A70" s="6"/>
+      <c r="B70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A71" s="6"/>
+      <c r="B71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A72" s="6"/>
+      <c r="B72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A73" s="6"/>
+      <c r="B73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A74" s="6"/>
+      <c r="B74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A75" s="6"/>
+      <c r="B75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A76" s="6"/>
+      <c r="B76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A77" s="6"/>
+      <c r="B77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A78" s="6"/>
+      <c r="B78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A79" s="6"/>
+      <c r="B79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A80" s="6"/>
+      <c r="B80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A81" s="6"/>
+      <c r="B81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A82" s="6"/>
+      <c r="B82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A83" s="6"/>
+      <c r="B83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A84" s="6"/>
+      <c r="B84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A85" s="6"/>
+      <c r="B85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A86" s="6"/>
+      <c r="B86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A87" s="6"/>
+      <c r="B87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A88" s="6"/>
+      <c r="B88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A89" s="6"/>
+      <c r="B89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A90" s="6"/>
+      <c r="B90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A91" s="6"/>
+      <c r="B91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A92" s="6"/>
+      <c r="B92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A93" s="6"/>
+      <c r="B93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A94" s="6"/>
+      <c r="B94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A95" s="6"/>
+      <c r="B95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A96" s="6"/>
+      <c r="B96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A97" s="6"/>
+      <c r="B97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A98" s="6"/>
+      <c r="B98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A99" s="6"/>
+      <c r="B99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A100" s="6"/>
+      <c r="B100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A101" s="6"/>
+      <c r="B101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A102" s="6"/>
+      <c r="B102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A103" s="6"/>
+      <c r="B103" s="2"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2"/>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A104" s="6"/>
+      <c r="B104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A105" s="6"/>
+      <c r="B105" s="2"/>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2"/>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A106" s="6"/>
+      <c r="B106" s="2"/>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A107" s="6"/>
+      <c r="B107" s="2"/>
+      <c r="D107" s="2"/>
+      <c r="E107" s="2"/>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A108" s="6"/>
+      <c r="B108" s="2"/>
+      <c r="D108" s="2"/>
+      <c r="E108" s="2"/>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A109" s="6"/>
+      <c r="B109" s="2"/>
+      <c r="D109" s="2"/>
+      <c r="E109" s="2"/>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A110" s="6"/>
+      <c r="B110" s="2"/>
+      <c r="D110" s="2"/>
+      <c r="E110" s="2"/>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A111" s="6"/>
+      <c r="B111" s="2"/>
+      <c r="D111" s="2"/>
+      <c r="E111" s="2"/>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A112" s="6"/>
+      <c r="B112" s="2"/>
+      <c r="D112" s="2"/>
+      <c r="E112" s="2"/>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A113" s="6"/>
+      <c r="B113" s="2"/>
+      <c r="D113" s="2"/>
+      <c r="E113" s="2"/>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A114" s="6"/>
+      <c r="B114" s="2"/>
+      <c r="D114" s="2"/>
+      <c r="E114" s="2"/>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A115" s="6"/>
+      <c r="B115" s="2"/>
+      <c r="D115" s="2"/>
+      <c r="E115" s="2"/>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A116" s="6"/>
+      <c r="B116" s="2"/>
+      <c r="D116" s="2"/>
+      <c r="E116" s="2"/>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A117" s="6"/>
+      <c r="B117" s="2"/>
+      <c r="D117" s="2"/>
+      <c r="E117" s="2"/>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A118" s="6"/>
+      <c r="B118" s="2"/>
+      <c r="D118" s="2"/>
+      <c r="E118" s="2"/>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A119" s="6"/>
+      <c r="B119" s="2"/>
+      <c r="D119" s="2"/>
+      <c r="E119" s="2"/>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A120" s="6"/>
+      <c r="B120" s="2"/>
+      <c r="D120" s="2"/>
+      <c r="E120" s="2"/>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A121" s="6"/>
+      <c r="B121" s="2"/>
+      <c r="D121" s="2"/>
+      <c r="E121" s="2"/>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A122" s="6"/>
+      <c r="B122" s="2"/>
+      <c r="D122" s="2"/>
+      <c r="E122" s="2"/>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A123" s="6"/>
+      <c r="B123" s="2"/>
+      <c r="D123" s="2"/>
+      <c r="E123" s="2"/>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A124" s="6"/>
+      <c r="B124" s="2"/>
+      <c r="D124" s="2"/>
+      <c r="E124" s="2"/>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A125" s="6"/>
+      <c r="B125" s="2"/>
+      <c r="D125" s="2"/>
+      <c r="E125" s="2"/>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A126" s="6"/>
+      <c r="B126" s="2"/>
+      <c r="D126" s="2"/>
+      <c r="E126" s="2"/>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A127" s="6"/>
+      <c r="B127" s="2"/>
+      <c r="D127" s="2"/>
+      <c r="E127" s="2"/>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A128" s="6"/>
+      <c r="B128" s="2"/>
+      <c r="D128" s="2"/>
+      <c r="E128" s="2"/>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A129" s="6"/>
+      <c r="B129" s="2"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="2"/>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A130" s="6"/>
+      <c r="B130" s="2"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="2"/>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A131" s="6"/>
+      <c r="B131" s="2"/>
+      <c r="D131" s="2"/>
+      <c r="E131" s="2"/>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A132" s="6"/>
+      <c r="B132" s="2"/>
+      <c r="D132" s="2"/>
+      <c r="E132" s="2"/>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A133" s="6"/>
+      <c r="B133" s="2"/>
+      <c r="D133" s="2"/>
+      <c r="E133" s="2"/>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A134" s="6"/>
+      <c r="B134" s="2"/>
+      <c r="D134" s="2"/>
+      <c r="E134" s="2"/>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A135" s="6"/>
+      <c r="B135" s="2"/>
+      <c r="D135" s="2"/>
+      <c r="E135" s="2"/>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A136" s="6"/>
+      <c r="B136" s="2"/>
+      <c r="D136" s="2"/>
+      <c r="E136" s="2"/>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A137" s="6"/>
+      <c r="B137" s="2"/>
+      <c r="D137" s="2"/>
+      <c r="E137" s="2"/>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A138" s="6"/>
+      <c r="B138" s="5"/>
+      <c r="D138" s="2"/>
+      <c r="E138" s="2"/>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="D139" s="2"/>
+      <c r="E139" s="2"/>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="D140" s="2"/>
+      <c r="E140" s="2"/>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="D141" s="2"/>
+      <c r="E141" s="2"/>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="D142" s="2"/>
+      <c r="E142" s="2"/>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="D143" s="5"/>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="D144" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E5" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <phoneticPr fontId="3"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力内容を確認してください" error="「はい」または「いいえ」を選択してください。分からない場合は空欄のままで構いません。" promptTitle="回答方法" prompt="「はい」または「いいえ」を選択。分からない場合は空欄。" sqref="C4 C2" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力内容を確認してください" error="「はい」または「いいえ」を選択してください。分からない場合は空欄のままで構いません。" promptTitle="回答方法" prompt="「はい」または「いいえ」を選択。分からない場合は空欄。" sqref="C4 C2 C6 C10:C11 C13" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"はい,いいえ"</formula1>
     </dataValidation>
   </dataValidations>
